--- a/rtss-pre1917/src/main/resources/census-1897/census-1897.xlsx
+++ b/rtss-pre1917/src/main/resources/census-1897/census-1897.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\census-1897\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED044646-6B9D-45E9-BB49-967A8DE5AB57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A800E22-1B3E-4505-AAD5-4583CA1953D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="82605" yWindow="0" windowWidth="31005" windowHeight="23295" activeTab="1" xr2:uid="{0CC79554-7499-452A-B074-39FD34D45BAD}"/>
+    <workbookView xWindow="78900" yWindow="1125" windowWidth="25950" windowHeight="16680" activeTab="1" xr2:uid="{0CC79554-7499-452A-B074-39FD34D45BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="115">
   <si>
     <t>губ</t>
   </si>
@@ -376,6 +376,12 @@
   </si>
   <si>
     <t>Европейская Poccия без Польши</t>
+  </si>
+  <si>
+    <t>Астраханская (оседлое население)</t>
+  </si>
+  <si>
+    <t>Астраханская (кочевники)</t>
   </si>
 </sst>
 </file>
@@ -425,14 +431,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -451,9 +456,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -491,7 +496,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -597,7 +602,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -739,7 +744,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -762,7 +767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BF2D5ED-C086-4B9A-AF7A-3CCA60AD96B2}">
-  <dimension ref="A1:I106"/>
+  <dimension ref="A1:I109"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="1" width="36.41796875" bestFit="1" customWidth="1"/>
@@ -799,15 +804,15 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="2">
         <f>B3+B60</f>
         <v>50461665</v>
       </c>
-      <c r="C2" s="6">
+      <c r="C2" s="2">
         <f>C3+C60</f>
         <v>52383452</v>
       </c>
-      <c r="D2" s="6">
+      <c r="D2" s="2">
         <f>D3+D60</f>
         <v>102845117</v>
       </c>
@@ -2952,8 +2957,30 @@
         <v>0</v>
       </c>
     </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>113</v>
+      </c>
+      <c r="D108" s="2">
+        <v>660173</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" t="s">
+        <v>114</v>
+      </c>
+      <c r="D109" s="2">
+        <v>343369</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{0cf7ac0a-4681-4823-ab0b-04ef02c5f873}" enabled="1" method="Standard" siteId="{42f7676c-f455-423c-82f6-dc2d99791af7}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/rtss-pre1917/src/main/resources/census-1897/census-1897.xlsx
+++ b/rtss-pre1917/src/main/resources/census-1897/census-1897.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\census-1897\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A800E22-1B3E-4505-AAD5-4583CA1953D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE39D829-B3DC-4979-8180-3591BF3AF5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="78900" yWindow="1125" windowWidth="25950" windowHeight="16680" activeTab="1" xr2:uid="{0CC79554-7499-452A-B074-39FD34D45BAD}"/>
+    <workbookView xWindow="64470" yWindow="3165" windowWidth="38700" windowHeight="14970" activeTab="1" xr2:uid="{0CC79554-7499-452A-B074-39FD34D45BAD}"/>
   </bookViews>
   <sheets>
     <sheet name="note" sheetId="1" r:id="rId1"/>
